--- a/ig/DM-JUIN-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -10522,7 +10522,7 @@
     <t>1578</t>
   </si>
   <si>
-    <t>Centre expert maladie de Parkinson</t>
+    <t>Centre expert en maladie de Parkinson</t>
   </si>
   <si>
     <t>1579</t>
@@ -11044,7 +11044,7 @@
     <t>1665</t>
   </si>
   <si>
-    <t>Evaluation orthoptique de la fonction visuelle et/ou prise en soins avec l'ajustement des aides optiques et nouvelles technologies dans le cadre d'handicap de la fonction visuelle (RV)</t>
+    <t>Evaluation orthoptique et/ou prise en soins avec ajustement d'aide optique et nouvelle technologie associé à un handicap de la fonction visuelle (RV)</t>
   </si>
   <si>
     <t>1666</t>

--- a/ig/DM-JUIN-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -9190,7 +9190,7 @@
     <t>1391</t>
   </si>
   <si>
-    <t>Prise en charge de ùaladies vectorielles à tique (Lyme…)</t>
+    <t>Prise en charge de maladies vectorielles à tique (Lyme…)</t>
   </si>
   <si>
     <t>Prise en charge des maladies infectieuses transmises par tiques (vecteur) qui assurent une transmission active d'un agent infectieux (par exemple la borréliose, responsable de la maladie de Lyme).</t>

--- a/ig/DM-JUIN-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -9190,7 +9190,7 @@
     <t>1391</t>
   </si>
   <si>
-    <t>Prise en charge de maladies vectorielles à tique (Lyme…)</t>
+    <t>Prise en charge de ùaladies vectorielles à tique (Lyme…)</t>
   </si>
   <si>
     <t>Prise en charge des maladies infectieuses transmises par tiques (vecteur) qui assurent une transmission active d'un agent infectieux (par exemple la borréliose, responsable de la maladie de Lyme).</t>
